--- a/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9446_escuela-de-parvulos-rayito-de-luz_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7ADC359-23D6-4A1B-9AE7-79F6F0C121DC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA722052-8D6C-44E9-8137-E57E9F3A1CCE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1E633E30-E5D2-4625-AB16-D7BABBA0557B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B0945CE1-A70A-4646-93F8-77C68CE8DED1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E547BF16-9690-46A2-A3B8-3A9383E8FFCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A4473C08-2D4C-4920-9AA4-8E5BCC48CB85}"/>
 </file>